--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.59868134380899</v>
+        <v>3.347285718368961</v>
       </c>
       <c r="D2" t="n">
-        <v>21.75309324735433</v>
+        <v>3.534877652695078</v>
       </c>
       <c r="E2" t="n">
-        <v>4.426245145571972</v>
+        <v>0.7192648361554455</v>
       </c>
       <c r="F2" t="n">
-        <v>4.490553780182361</v>
+        <v>0.7297149892796336</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.60004874190671</v>
+        <v>2.04750792055984</v>
       </c>
       <c r="D3" t="n">
-        <v>10.8785395343476</v>
+        <v>1.767762674331485</v>
       </c>
       <c r="E3" t="n">
-        <v>4.426245145571972</v>
+        <v>0.7192648361554455</v>
       </c>
       <c r="F3" t="n">
-        <v>4.490553780182361</v>
+        <v>0.7297149892796336</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.11831272297319</v>
+        <v>2.131725817483144</v>
       </c>
       <c r="D4" t="n">
-        <v>11.72685826398801</v>
+        <v>1.905614467898052</v>
       </c>
       <c r="E4" t="n">
-        <v>4.426245145571972</v>
+        <v>0.7192648361554455</v>
       </c>
       <c r="F4" t="n">
-        <v>4.490553780182361</v>
+        <v>0.7297149892796336</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.78365575379726</v>
+        <v>2.077344059992055</v>
       </c>
       <c r="D5" t="n">
-        <v>11.15602024528218</v>
+        <v>1.812853289858354</v>
       </c>
       <c r="E5" t="n">
-        <v>4.426245145571972</v>
+        <v>0.7192648361554455</v>
       </c>
       <c r="F5" t="n">
-        <v>4.490553780182361</v>
+        <v>0.7297149892796336</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.8840038220938</v>
+        <v>3.718650621090243</v>
       </c>
       <c r="D6" t="n">
-        <v>9.164960653336564</v>
+        <v>1.489306106167192</v>
       </c>
       <c r="E6" t="n">
-        <v>4.426245145571972</v>
+        <v>0.7192648361554455</v>
       </c>
       <c r="F6" t="n">
-        <v>4.490553780182361</v>
+        <v>0.7297149892796336</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
